--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/GANDHINAGAR.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/GANDHINAGAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE90A7D-1558-433B-B8A3-B38514806730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0F75ED-EC66-4DBD-BC43-DF03E47BAE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="375" windowWidth="14940" windowHeight="15255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -462,43 +462,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -510,7 +487,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -793,115 +793,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-    </row>
-    <row r="3" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="30">
         <v>6</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22">
+      <c r="E4" s="30"/>
+      <c r="F4" s="30">
         <v>6</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22">
+      <c r="G4" s="30"/>
+      <c r="H4" s="30">
         <v>6</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22">
+      <c r="I4" s="30"/>
+      <c r="J4" s="30">
         <v>8</v>
       </c>
-      <c r="K4" s="22"/>
+      <c r="K4" s="30"/>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="23" t="s">
+    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="17"/>
+      <c r="F5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="28" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="28" t="s">
+      <c r="I5" s="22"/>
+      <c r="J5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="29"/>
+      <c r="K5" s="22"/>
       <c r="L5" s="9">
         <f>D4+F4+H4+J4</f>
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -937,7 +937,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>18</v>
       </c>
@@ -965,7 +965,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="11"/>
     </row>
-    <row r="8" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>43</v>
       </c>
@@ -985,7 +985,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="11"/>
     </row>
-    <row r="9" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>22</v>
       </c>
@@ -1013,7 +1013,7 @@
       <c r="K9" s="12"/>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1037,7 +1037,7 @@
       <c r="K10" s="12"/>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+    <row r="12" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="1">
         <f>SUM(D7:D11)</f>
         <v>4</v>
@@ -1100,23 +1100,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-    </row>
-    <row r="14" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+    </row>
+    <row r="14" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
@@ -1140,11 +1140,11 @@
       </c>
       <c r="L14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="L15" s="11"/>
     </row>
-    <row r="16" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>28</v>
       </c>
@@ -1188,7 +1188,7 @@
       <c r="K16" s="13"/>
       <c r="L16" s="11"/>
     </row>
-    <row r="17" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>28</v>
       </c>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="L17" s="11"/>
     </row>
-    <row r="18" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>28</v>
       </c>
@@ -1236,12 +1236,12 @@
       <c r="K18" s="13"/>
       <c r="L18" s="11"/>
     </row>
-    <row r="19" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+    <row r="19" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="24"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="1">
         <f>SUM(D14:D18)</f>
         <v>2</v>
@@ -1267,12 +1267,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+    <row r="20" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="24"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="17"/>
       <c r="D20" s="1">
         <f>+D12+D19</f>
         <v>6</v>
@@ -1300,13 +1300,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -1317,6 +1310,13 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1326,115 +1326,115 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-    </row>
-    <row r="3" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="30">
         <v>4</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22">
+      <c r="E4" s="30"/>
+      <c r="F4" s="30">
         <v>4</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22">
+      <c r="G4" s="30"/>
+      <c r="H4" s="30">
         <v>4</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22">
+      <c r="I4" s="30"/>
+      <c r="J4" s="30">
         <v>4</v>
       </c>
-      <c r="K4" s="22"/>
+      <c r="K4" s="30"/>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="23" t="s">
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="17"/>
+      <c r="F5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="28" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="28" t="s">
+      <c r="I5" s="22"/>
+      <c r="J5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="29"/>
+      <c r="K5" s="22"/>
       <c r="L5" s="2">
         <f>D4+F4+H4+J4</f>
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L7" s="11"/>
     </row>
-    <row r="8" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="11"/>
     </row>
-    <row r="9" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>22</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="K9" s="12"/>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>28</v>
       </c>
@@ -1602,12 +1602,12 @@
       <c r="K11" s="12"/>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+    <row r="12" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="1">
         <f>SUM(D7:D11)</f>
         <v>4</v>
@@ -1633,28 +1633,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-    </row>
-    <row r="14" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+    </row>
+    <row r="14" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="24"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="1">
         <v>0</v>
       </c>
@@ -1675,12 +1675,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="24"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="1">
         <f>+D12+D14</f>
         <v>4</v>
@@ -1708,14 +1708,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -1725,6 +1717,14 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
